--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_647_Russia_Black_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_647_Russia_Black_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rbdf187496c454603"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2db2aa7cac5748f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R26757ad98bb24e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra310ffd4dc2b43f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5d2521263e974e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd673261b9bc14f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rce01d590dcff43bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6826895e9ec34cb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0cefe5b80eb9401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re729b2e68b5d4fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R96be657b73da4ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R35e79ef6541442f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ647CommercialTable" displayName="EEZ647CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ647CommercialTable" displayName="EEZ647CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ647FunctionalTable" displayName="EEZ647FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ647FunctionalTable" displayName="EEZ647FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ647ValidationTable" displayName="EEZ647ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ647ValidationTable" displayName="EEZ647ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3374,7 +3328,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38fd5d2d8fc14e8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7788a1f890f4d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3384,20 +3338,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3405,714 +3349,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>70165.79548236</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>70165.79548236</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$41,A2,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>9039105.457434237</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>9039105.457434237</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1939.647538725</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1939.647538725</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$41,A3,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4443475.804235732</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4443475.804235732</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1637.7274376392002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.8465528989928437</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>70.23488877334256</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1637.7274376392002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>91.90854357279332</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$41,A4,'Species'!$U$2:$U$41))</x:f>
-        <x:v>150521.14356262158</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.8465528989928437</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>70.23488877334256</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>115025.60442364054</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>35495.53913898104</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3085881558009518</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.3085881558009518</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>884.9812383069</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.885278420895203</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>767.8535931770657</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>884.9812383069</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1137.5150970817683</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$41,A5,'Species'!$U$2:$U$41))</x:f>
-        <x:v>1006679.5192082168</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.885278420895203</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>767.8535931770657</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>679536.0237282423</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>327143.49547997455</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.4814218585279957</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.4814218585279957</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>34887.7595025061</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.017553642559179</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>104.1246710889697</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>34887.7595025061</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>109.8506517557637</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$41,A6,'Species'!$U$2:$U$41))</x:f>
-        <x:v>3832443.119648634</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.017553642559179</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>104.1246710889697</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3632676.4832295254</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>199766.6364191086</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.054991584673544</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.05499158467354403</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>366.3050517662</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.69</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>48.97788193684461</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>366.3050517662</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>48.97788193684461</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$41,A7,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>17940.845578274697</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.69</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>48.97788193684461</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>17940.845578274697</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>15671.3705385095</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.203849972762083</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>159.90055559548503</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>15671.3705385095</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>175.49023634274826</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$41,A8,'Species'!$U$2:$U$41))</x:f>
-        <x:v>2750172.519617814</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.203849972762083</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>159.90055559548503</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2505860.8560503847</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>244311.6635674294</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.097496101181173</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.09749610118117312</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>23564.9454957405</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2398622746094845</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>173.72498170244026</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>23564.9454957405</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>272.4124462134531</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$41,A9,'Species'!$U$2:$U$41))</x:f>
-        <x:v>6419384.447381362</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2398622746094845</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>173.72498170244026</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4093819.7250665203</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2325564.722314842</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.568067203368867</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.568067203368867</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>48.8472323301</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.07</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1174.8975549395302</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>48.8472323301</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1174.8975549395302</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$41,A10,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>57390.49383019766</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.07</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1174.8975549395302</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>57390.49383019766</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>529.7486380321</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8703775375444907</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>741.9549516148068</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>529.7486380321</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>741.9932333715553</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$41,A11,'Species'!$U$2:$U$41))</x:f>
-        <x:v>393069.90480761556</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8703775375444907</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>741.9549516148068</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>393049.6250991165</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>20.279708499030676</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0000515957965712</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.00005159579657127692</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1904.0852989260998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.7716586399258554</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>591.0968431390443</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1904.0852989260998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>957.0710087325651</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$41,A12,'Species'!$U$2:$U$41))</x:f>
-        <x:v>1822344.83775605</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.7716586399258554</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>591.0968431390443</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1125498.809262681</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>696846.028493369</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.619144172129223</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.619144172129223</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>170.2418964819</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>170.2418964819</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>3162.27766016838</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$41,A13,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>538352.1460694103</x:v>
       </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>538352.1460694103</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb13d672f7d7340ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73abe1fcb6c1448a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4122,20 +3602,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4143,1038 +3613,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>597</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.1446231155778896</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>13.951571064344368</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>14.311438221424124</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$41,A2,'Species'!$U$2:$U$41))</x:f>
-        <x:v>8543.928618190203</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.1446231155778896</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>13.951571064344368</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>8329.087925413587</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>214.84069277661547</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.025794023871581</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.02579402387158104</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>61.2321485842</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9749370179878194</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>943.9239771428512</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>61.2321485842</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1017.7826393264991</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$41,A3,'Species'!$U$2:$U$41))</x:f>
-        <x:v>62321.01779765943</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9749370179878194</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>943.9239771428512</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>57798.49322060007</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>4522.524577059361</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0782464096390576</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0782464096390575</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>353.18416118389996</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>353.18416118389996</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$41,A4,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>809098.1703261164</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>809098.1703261164</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>437.1987907883</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.53</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>3388.4415613920273</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>437.1987907883</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$41,A5,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1481422.5532974135</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.53</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>1481422.5532974135</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1239.9912485128</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.481845586384548</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>303.28126744435644</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1239.9912485128</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>331.17357152344727</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$41,A6,'Species'!$U$2:$U$41))</x:f>
-        <x:v>410652.33042780246</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.481845586384548</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>303.28126744435644</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>376066.11746887193</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>34586.212958930526</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0919684368049811</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.09196843680498104</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>529.7486380321</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8703775375444907</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>741.9549516148068</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>529.7486380321</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>741.9932333715553</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$41,A7,'Species'!$U$2:$U$41))</x:f>
-        <x:v>393069.90480761556</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8703775375444907</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>741.9549516148068</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>393049.6250991165</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>20.279708499030676</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000515957965712</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00005159579657127692</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>664.0940504133</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.312795320599835</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2054.921900023958</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>664.0940504133</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2125.741837996709</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$41,A8,'Species'!$U$2:$U$41))</x:f>
-        <x:v>1411692.5073282474</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.312795320599835</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2054.921900023958</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1364661.4078699048</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>47031.09945834265</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0344635667038855</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.03446356670388542</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>272.0000000002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.43</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>269.1534803926917</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>272.0000000002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>269.1534803926917</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$41,A9,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>73209.74666686596</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.43</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>269.1534803926917</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>73209.74666686596</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3893.2077279249997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6625163688259503</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>459.74431625017286</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3893.2077279249997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1188.1700059053499</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$41,A10,'Species'!$U$2:$U$41))</x:f>
-        <x:v>4625792.649079401</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6625163688259503</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>459.74431625017286</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1789880.124894768</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2835912.524184633</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>2.584414779929111</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>1.5844147799291106</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>14744.689702614</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.2384491308985113</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>173.16061950847302</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>14744.689702614</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>180.27578151480114</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$41,A11,'Species'!$U$2:$U$41))</x:f>
-        <x:v>2658110.4593319795</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.2384491308985113</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>173.16061950847302</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2553199.603364843</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>104910.85596713657</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0410899546705534</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0410899546705535</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>5582.3526573071</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.738755068111189</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>547.9678367670915</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>5582.3526573071</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>610.618086668103</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$41,A12,'Species'!$U$2:$U$41))</x:f>
-        <x:v>3408685.4987114626</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.738755068111189</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>547.9678367670915</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3058949.7096955967</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>349735.7890158659</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1143319839183197</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.11433198391831977</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.21250806009999998</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.21250806009999998</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$41,A13,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>7.20071142973634</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>7.20071142973634</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1056.3050517664</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.5201626980766103</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>33.12551951041911</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1056.3050517664</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>34.56618489546944</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$41,A14,'Species'!$U$2:$U$41))</x:f>
-        <x:v>36512.435725375806</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.5201626980766103</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>33.12551951041911</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>34990.65360124216</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1521.7821241336496</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.043491103123596</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.04349110312359603</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1365.727437639</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.7303528380579825</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>53.74682795804299</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1365.727437639</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>56.608218276267195</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$41,A15,'Species'!$U$2:$U$41))</x:f>
-        <x:v>77311.3968957556</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.7303528380579825</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>53.74682795804299</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>73403.51762836223</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>3907.8792673933785</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0532383105558885</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.05323831055588842</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2008.4609442792</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.2769350939585244</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>189.20608258377766</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2008.4609442792</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>242.274910283875</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$41,A16,'Species'!$U$2:$U$41))</x:f>
-        <x:v>486599.69508391</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.2769350939585244</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>189.20608258377766</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>380013.02728958236</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>106586.66779432766</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2804816154713168</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2804816154713168</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>104732.30720017402</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.0765380057820932</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>119.2718637942368</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>104732.30720017402</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>119.97364663560103</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$41,A17,'Species'!$U$2:$U$41))</x:f>
-        <x:v>12565116.815364892</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.0765380057820932</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>119.2718637942368</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>12491617.479235321</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>73499.33612957038</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0058838926385432</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.005883892638543209</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>13701.946006921</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>13701.946006921</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$41,A18,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1765152.58007395</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>1765152.58007395</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>531.797077123</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>531.797077123</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$41,A19,'Species'!$U$2:$U$41))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>197581.3488821005</x:v>
       </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>197581.3488821005</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6231cbac0ad54d12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R453bfd3f707541a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5349,7 +4145,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5448,7 +4244,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>30470880.239130165</x:v>
+        <x:v>26641731.874007963</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5462,7 +4258,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>30470880.23913017</x:v>
+        <x:v>26908430.4472515</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5476,7 +4272,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-3829148.365122203</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5490,7 +4286,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-3562449.7918786667</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5501,9 +4297,9 @@
         <x:v>EEZ_647</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5515,47 +4311,19 @@
         <x:v>EEZ_647</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_647</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_647</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5a04ef1f5024ce4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45ec608f9997469a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5602,7 +4370,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
